--- a/artfynd/A 3474-2026 artfynd.xlsx
+++ b/artfynd/A 3474-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4193370</v>
+        <v>4158097</v>
       </c>
       <c r="B3" t="n">
-        <v>97517</v>
+        <v>97511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,23 +787,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -870,6 +866,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4193370</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97517</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SVEDJAN.S om.Skog, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>379064</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6391504</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1988-11-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1988-11-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Leif-eric Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Västergötlands flora 2002</t>
         </is>

--- a/artfynd/A 3474-2026 artfynd.xlsx
+++ b/artfynd/A 3474-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -971,6 +971,244 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131444632</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svedjan, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>379021</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6391535</v>
+      </c>
+      <c r="S5" t="n">
+        <v>33</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131444631</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svedjan, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>379021</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6391535</v>
+      </c>
+      <c r="S6" t="n">
+        <v>33</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3474-2026 artfynd.xlsx
+++ b/artfynd/A 3474-2026 artfynd.xlsx
@@ -977,7 +977,7 @@
         <v>131444632</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3474-2026 artfynd.xlsx
+++ b/artfynd/A 3474-2026 artfynd.xlsx
@@ -977,7 +977,7 @@
         <v>131444632</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131444631</v>
       </c>
       <c r="B6" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3474-2026 artfynd.xlsx
+++ b/artfynd/A 3474-2026 artfynd.xlsx
@@ -977,7 +977,7 @@
         <v>131444632</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131444631</v>
       </c>
       <c r="B6" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3474-2026 artfynd.xlsx
+++ b/artfynd/A 3474-2026 artfynd.xlsx
@@ -977,7 +977,7 @@
         <v>131444632</v>
       </c>
       <c r="B5" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131444631</v>
       </c>
       <c r="B6" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3474-2026 artfynd.xlsx
+++ b/artfynd/A 3474-2026 artfynd.xlsx
@@ -977,7 +977,7 @@
         <v>131444632</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131444631</v>
       </c>
       <c r="B6" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3474-2026 artfynd.xlsx
+++ b/artfynd/A 3474-2026 artfynd.xlsx
@@ -977,7 +977,7 @@
         <v>131444632</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131444631</v>
       </c>
       <c r="B6" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3474-2026 artfynd.xlsx
+++ b/artfynd/A 3474-2026 artfynd.xlsx
@@ -977,7 +977,7 @@
         <v>131444632</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131444631</v>
       </c>
       <c r="B6" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3474-2026 artfynd.xlsx
+++ b/artfynd/A 3474-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4236315</v>
+        <v>131444632</v>
       </c>
       <c r="B2" t="n">
-        <v>97520</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SVEDJAN.S om.Skog, Vg</t>
+          <t>Svedjan, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379064</v>
+        <v>379021</v>
       </c>
       <c r="R2" t="n">
-        <v>6391504</v>
+        <v>6391535</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1988-11-12</t>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1988-11-12</t>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,26 +782,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Leif-eric Aronsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4158097</v>
+        <v>131444631</v>
       </c>
       <c r="B3" t="n">
-        <v>97511</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,33 +805,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SVEDJAN.S om.Skog, Vg</t>
+          <t>Svedjan, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379064</v>
+        <v>379021</v>
       </c>
       <c r="R3" t="n">
-        <v>6391504</v>
+        <v>6391535</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1988-11-12</t>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1988-11-12</t>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,26 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Leif-eric Aronsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4193370</v>
+        <v>4158097</v>
       </c>
       <c r="B4" t="n">
-        <v>97517</v>
+        <v>97977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,23 +924,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -974,60 +1010,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131444632</v>
+        <v>4193370</v>
       </c>
       <c r="B5" t="n">
-        <v>57909</v>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svedjan, Vg</t>
+          <t>SVEDJAN.S om.Skog, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379021</v>
+        <v>379064</v>
       </c>
       <c r="R5" t="n">
-        <v>6391535</v>
+        <v>6391504</v>
       </c>
       <c r="S5" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1075,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>1988-11-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>1988-11-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1095,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Leif-eric Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131444631</v>
+        <v>4236315</v>
       </c>
       <c r="B6" t="n">
-        <v>57100</v>
+        <v>97986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,49 +1122,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svedjan, Vg</t>
+          <t>SVEDJAN.S om.Skog, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379021</v>
+        <v>379064</v>
       </c>
       <c r="R6" t="n">
-        <v>6391535</v>
+        <v>6391504</v>
       </c>
       <c r="S6" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,22 +1176,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>1988-11-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>1988-11-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,15 +1196,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Leif-eric Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3474-2026 artfynd.xlsx
+++ b/artfynd/A 3474-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444632</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444631</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4158097</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4193370</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,8 +1234,20 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4236315</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>